--- a/Plants.xlsx
+++ b/Plants.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruna\OneDrive\DOUTORADO\0.TESE\modelagem\modelo_bru\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ead127730922d462/DOUTORADO/0.TESE/modelagem/modelo_bru/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B62E733F-E2E4-4012-8470-C1B541D273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{B62E733F-E2E4-4012-8470-C1B541D273FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53B9FBC-2CC4-46E1-A186-98229D427486}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1683CF16-D6CE-428F-8B93-DD97FDAC2386}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -190,7 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -204,6 +204,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,11 +540,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFE9D97-E7E6-401A-8B63-E7AB508DAAF6}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.88671875" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
@@ -964,6 +965,12 @@
         <v>1037.3134</v>
       </c>
     </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G20" s="5">
+        <f>SUM(G2:G18)</f>
+        <v>43237.313399999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
